--- a/Documents/Sprint 1/UserStories_AcceptanceCriteria/UserStories_Sprint_1.xlsx
+++ b/Documents/Sprint 1/UserStories_AcceptanceCriteria/UserStories_Sprint_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Capstone\S2026A-Team2\Documents\Sprint 1\UserStories_AcceptanceCriteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C93BF18F-1DEA-4F01-B4DF-05ACEFC2DF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{030CA943-3126-4F40-AAEF-E13767735D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{25DEA90A-A52D-4471-A6A4-98AAF3EEC726}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>Assignee</t>
   </si>
@@ -186,6 +186,27 @@
   </si>
   <si>
     <t>Meghana/ Priya</t>
+  </si>
+  <si>
+    <t>US_02</t>
+  </si>
+  <si>
+    <t>US_03</t>
+  </si>
+  <si>
+    <t>US_04</t>
+  </si>
+  <si>
+    <t>US_05</t>
+  </si>
+  <si>
+    <t>US_06</t>
+  </si>
+  <si>
+    <t>US_07</t>
+  </si>
+  <si>
+    <t>US_08</t>
   </si>
 </sst>
 </file>
@@ -679,13 +700,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1068,7 +1089,7 @@
     <col min="1" max="1" width="8.53125" customWidth="1"/>
     <col min="2" max="2" width="46.59765625" customWidth="1"/>
     <col min="3" max="3" width="39.9296875" customWidth="1"/>
-    <col min="4" max="4" width="32.53125" customWidth="1"/>
+    <col min="4" max="4" width="22.46484375" customWidth="1"/>
     <col min="5" max="5" width="21.796875" customWidth="1"/>
     <col min="6" max="6" width="14.3984375" customWidth="1"/>
     <col min="7" max="7" width="17.3984375" customWidth="1"/>
@@ -1101,165 +1122,183 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="4">
         <v>55</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="171" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="4">
         <v>55</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="199.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="4" t="s">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="4">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="156.75" x14ac:dyDescent="0.45">
-      <c r="B5" s="4" t="s">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="4">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="4" t="s">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="4">
         <v>55</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B7" s="4" t="s">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="4">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="4" t="s">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="4">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B9" s="4" t="s">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="4">
         <v>21</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
